--- a/astro-site/public/dl/manual-chef-ejecutivo/desarrollo-carta-control-calidad.xlsx
+++ b/astro-site/public/dl/manual-chef-ejecutivo/desarrollo-carta-control-calidad.xlsx
@@ -973,16 +973,16 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>46273</v>
+        <v>46238</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>46280</v>
+        <v>46245</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>46287</v>
+        <v>46256</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>46294</v>
+        <v>46265</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>46301</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="K13" s="12">
         <f>IFERROR(IF(OR($D13="",$C$7=""),"",IF($C$7&lt;$D13,"",$C$7-$D13)),"")</f>
-        <v>16.0</v>
+        <v>51.0</v>
       </c>
       <c r="L13" s="12">
         <f>COUNT($D13:$H13)</f>
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="D14" s="6" t="n">
-        <v>46275</v>
+        <v>46240</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>46282</v>
+        <v>46247</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>46289</v>
+        <v>46258</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>46296</v>
+        <v>46267</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>46301</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="K14" s="12">
         <f>IFERROR(IF(OR($D14="",$C$7=""),"",IF($C$7&lt;$D14,"",$C$7-$D14)),"")</f>
-        <v>14.0</v>
+        <v>49.0</v>
       </c>
       <c r="L14" s="12">
         <f>COUNT($D14:$H14)</f>
